--- a/labs/lab-01-excel-to-word/data/checkpoints/Northstar_Verified_Checkpoint.xlsx
+++ b/labs/lab-01-excel-to-word/data/checkpoints/Northstar_Verified_Checkpoint.xlsx
@@ -13,15 +13,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Control" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prompt_Log" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Checks" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Evidence_Log" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'About_This_Data'!$A$1:$B$6</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Work_Orders'!$A$1:$M$121</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Technicians'!$A$1:$D$9</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Control'!$A$1:$B$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Prompt_Log'!$A$1:$F$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Checks'!$A$1:$C$2</definedName>
-  </definedNames>
+  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -561,7 +555,6 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B6"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1331,7 +1324,7 @@
           <t>New</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr"/>
+      <c r="F14" s="2"/>
       <c r="G14" s="4" t="n">
         <v>46278</v>
       </c>
@@ -1971,7 +1964,7 @@
           <t>New</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr"/>
+      <c r="F26" s="2"/>
       <c r="G26" s="4" t="n">
         <v>46266</v>
       </c>
@@ -3259,7 +3252,7 @@
           <t>New</t>
         </is>
       </c>
-      <c r="F50" s="2" t="inlineStr"/>
+      <c r="F50" s="2"/>
       <c r="G50" s="4" t="n">
         <v>46242</v>
       </c>
@@ -4547,7 +4540,7 @@
           <t>New</t>
         </is>
       </c>
-      <c r="F74" s="2" t="inlineStr"/>
+      <c r="F74" s="2"/>
       <c r="G74" s="4" t="n">
         <v>46218</v>
       </c>
@@ -5187,7 +5180,7 @@
           <t>New</t>
         </is>
       </c>
-      <c r="F86" s="2" t="inlineStr"/>
+      <c r="F86" s="2"/>
       <c r="G86" s="4" t="n">
         <v>46286</v>
       </c>
@@ -6475,7 +6468,7 @@
           <t>New</t>
         </is>
       </c>
-      <c r="F110" s="2" t="inlineStr"/>
+      <c r="F110" s="2"/>
       <c r="G110" s="4" t="n">
         <v>46262</v>
       </c>
@@ -7090,7 +7083,6 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M121"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -7296,7 +7288,6 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D9"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -7478,7 +7469,6 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B15"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -7643,7 +7633,6 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -7687,12 +7676,82 @@
       </c>
       <c r="B2" s="2">
         <f>ROWS(tblWorkOrders[Work_Order_ID])</f>
-        <v/>
-      </c>
-      <c r="C2" s="2" t="inlineStr"/>
+      </c>
+      <c r="C2" s="2"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C2"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="17" customWidth="1" min="1" max="1"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="4" max="4"/>
+    <col width="17" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="17" customWidth="1" min="7" max="7"/>
+    <col width="17" customWidth="1" min="8" max="8"/>
+    <col width="17" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Lab</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Step</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Claim_or_Test</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Expected</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Observed</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Source_and_Scope</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>As_At</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Verified_By</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>